--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\2_Produccion\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\motaro\Indices\IPC\Difusión\2_Produccion\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141F4F49-07B2-44A5-BD94-452C6AB8F67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B89094-C98C-4424-B1F8-B673BB48ECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 6 de Febrero de 2026</t>
+    <t>Actualizado el 6 de Marzo de 2026</t>
   </si>
 </sst>
 </file>
@@ -2055,7 +2055,9 @@
       <c r="X11" s="35">
         <v>147.9</v>
       </c>
-      <c r="Y11" s="32"/>
+      <c r="Y11" s="32">
+        <v>155.72999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">

--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\motaro\Indices\IPC\Difusión\2_Produccion\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\motaro\Indices\IPC\Difusión\3_Revision\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B89094-C98C-4424-B1F8-B673BB48ECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D621B227-09BA-4A5A-92FE-EF00C6B5F0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -126,7 +129,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 6 de Marzo de 2026</t>
+    <t>Actualizado el 9 de Abril de 2026</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2135,9 @@
       <c r="X12" s="13">
         <v>148.68</v>
       </c>
-      <c r="Y12" s="39"/>
+      <c r="Y12" s="39">
+        <v>156.94</v>
+      </c>
     </row>
     <row r="13" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
@@ -3056,18 +3061,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3089,6 +3094,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CEC6C9-CA48-4E93-BC99-F210F33FD8FB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3102,12 +3115,4 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\motaro\Indices\IPC\Difusión\3_Revision\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\TRABAJO ABRIL 2026\CALCULO ABRIL\10. PRODUCTO ANEXO VARIACIONES\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D621B227-09BA-4A5A-92FE-EF00C6B5F0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF4C324-240B-47F1-A1A8-11143DAD5C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -129,7 +126,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 9 de Abril de 2026</t>
+    <t>Actualizado el 8 de Mayo de 2026</t>
   </si>
 </sst>
 </file>
@@ -2212,7 +2209,9 @@
       <c r="X13" s="14">
         <v>149.66</v>
       </c>
-      <c r="Y13" s="26"/>
+      <c r="Y13" s="26">
+        <v>158.16999999999999</v>
+      </c>
       <c r="AA13" s="49"/>
     </row>
     <row r="14" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -2917,6 +2916,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027BDBDF69F845F4383C93D67CEBAFF04" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0ea007cbf4cb5b5cc813a7650d64ca58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb0b624f-ae06-4913-a28b-bf5d24a61ccb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b65969171b7152b51da7f3e00aa75fb" ns2:_="">
     <xsd:import namespace="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
@@ -3060,22 +3074,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CEC6C9-CA48-4E93-BC99-F210F33FD8FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85115342-A464-41ED-B238-9E002ED72CDD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3091,28 +3114,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CEC6C9-CA48-4E93-BC99-F210F33FD8FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\TRABAJO ABRIL 2026\CALCULO ABRIL\10. PRODUCTO ANEXO VARIACIONES\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\RO-IPC-06-26\Producción\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF4C324-240B-47F1-A1A8-11143DAD5C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2177DF11-D1DB-49B9-BAE3-EB1D9D419B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndicesIPC" sheetId="520" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -126,7 +113,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 8 de Mayo de 2026</t>
+    <t>Actualizado el 5 de Junio de 2026</t>
   </si>
 </sst>
 </file>
@@ -2287,7 +2274,9 @@
       <c r="X14" s="13">
         <v>150.13999999999999</v>
       </c>
-      <c r="Y14" s="39"/>
+      <c r="Y14" s="39">
+        <v>158.91</v>
+      </c>
     </row>
     <row r="15" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">

--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\RO-IPC-06-26\Producción\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\RO-IPC-07-26\Producción\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2177DF11-D1DB-49B9-BAE3-EB1D9D419B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51C2A6AD-C825-4B7F-A946-B2E3C61CF4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndicesIPC" sheetId="520" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -113,7 +126,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 5 de Junio de 2026</t>
+    <t>Actualizado el 7 de Julio de 2026</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1649,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" style="8" customWidth="1"/>
@@ -1645,7 +1658,7 @@
     <col min="26" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="55"/>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -1672,8 +1685,8 @@
       <c r="X1" s="55"/>
       <c r="Y1" s="55"/>
     </row>
-    <row r="2" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:27" s="6" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:28" s="6" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="56" t="s">
         <v>15</v>
       </c>
@@ -1702,7 +1715,7 @@
       <c r="X3" s="56"/>
       <c r="Y3" s="56"/>
     </row>
-    <row r="4" spans="1:27" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="56"/>
       <c r="B4" s="56"/>
       <c r="C4" s="56"/>
@@ -1729,7 +1742,7 @@
       <c r="X4" s="56"/>
       <c r="Y4" s="56"/>
     </row>
-    <row r="5" spans="1:27" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="57" t="s">
         <v>17</v>
       </c>
@@ -1758,8 +1771,8 @@
       <c r="X5" s="58"/>
       <c r="Y5" s="58"/>
     </row>
-    <row r="6" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:27" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:28" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1786,7 +1799,7 @@
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
     </row>
-    <row r="8" spans="1:27" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1815,7 +1828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,7 +1905,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -1969,7 +1982,7 @@
         <v>154.07</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
@@ -2046,7 +2059,7 @@
         <v>155.72999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,7 +2136,7 @@
         <v>156.94</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="AA13" s="49"/>
     </row>
-    <row r="14" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -2278,7 +2291,7 @@
         <v>158.91</v>
       </c>
     </row>
-    <row r="15" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -2351,9 +2364,12 @@
       <c r="X15" s="14">
         <v>150.30000000000001</v>
       </c>
-      <c r="Y15" s="26"/>
+      <c r="Y15" s="26">
+        <v>159.53</v>
+      </c>
+      <c r="AB15" s="49"/>
     </row>
-    <row r="16" spans="1:27" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
@@ -2911,15 +2927,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027BDBDF69F845F4383C93D67CEBAFF04" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0ea007cbf4cb5b5cc813a7650d64ca58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb0b624f-ae06-4913-a28b-bf5d24a61ccb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b65969171b7152b51da7f3e00aa75fb" ns2:_="">
     <xsd:import namespace="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
@@ -3063,6 +3070,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CEC6C9-CA48-4E93-BC99-F210F33FD8FB}">
   <ds:schemaRefs>
@@ -3080,14 +3096,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85115342-A464-41ED-B238-9E002ED72CDD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3103,4 +3111,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\RO-IPC-07-26\Producción\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\IPC\2026\Julio 26\Calculo\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51C2A6AD-C825-4B7F-A946-B2E3C61CF4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05369FDB-2AD9-4A0E-8F71-1AB3588BAC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 7 de Julio de 2026</t>
+    <t>Actualizado el 10 de Agosto de 2026</t>
   </si>
 </sst>
 </file>
@@ -2442,7 +2442,9 @@
       <c r="X16" s="13">
         <v>150.71</v>
       </c>
-      <c r="Y16" s="40"/>
+      <c r="Y16" s="40">
+        <v>159.79</v>
+      </c>
     </row>
     <row r="17" spans="1:25" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">

--- a/update/historicos/ipc_colombia.xlsx
+++ b/update/historicos/ipc_colombia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calculo\Desktop\IPC\2026\Julio 26\Calculo\Indices. Series de empalme  2003 - 2019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\2_Produccion\7_Anexos\B. INDICES Y PONDERACIONES\Indices. Series de empalme  2003 - 2019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05369FDB-2AD9-4A0E-8F71-1AB3588BAC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C7E6B5-297A-4AA8-907F-A434A0D219A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -126,7 +129,7 @@
 2003 - 2026</t>
   </si>
   <si>
-    <t>Actualizado el 10 de Agosto de 2026</t>
+    <t>Actualizado el 7 de Septiembre de 2026</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2522,9 @@
       <c r="X17" s="14">
         <v>150.99</v>
       </c>
-      <c r="Y17" s="41"/>
+      <c r="Y17" s="41">
+        <v>160.41999999999999</v>
+      </c>
     </row>
     <row r="18" spans="1:25" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
@@ -2923,12 +2928,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010027BDBDF69F845F4383C93D67CEBAFF04" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0ea007cbf4cb5b5cc813a7650d64ca58">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb0b624f-ae06-4913-a28b-bf5d24a61ccb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b65969171b7152b51da7f3e00aa75fb" ns2:_="">
     <xsd:import namespace="bb0b624f-ae06-4913-a28b-bf5d24a61ccb"/>
@@ -3072,16 +3086,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6CEC6C9-CA48-4E93-BC99-F210F33FD8FB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3097,7 +3110,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85115342-A464-41ED-B238-9E002ED72CDD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3113,12 +3126,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D72D454-867A-47C4-AB39-812B39DB7663}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>